--- a/K-mean練習題/上課範例2.使用Excel計算分群-20筆.xlsx
+++ b/K-mean練習題/上課範例2.使用Excel計算分群-20筆.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.教學\3.資料探勘DataMining\K-mean練習題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.教學\3.資料探勘DataMining\Data Mining MarkDown\K-mean練習題\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
-    <sheet name="工作表3" sheetId="3" r:id="rId3"/>
-    <sheet name="工作表4" sheetId="4" r:id="rId4"/>
-    <sheet name="工作表5" sheetId="5" r:id="rId5"/>
+    <sheet name="題目" sheetId="1" r:id="rId1"/>
+    <sheet name="第一次計算形心_及與樣本的距離" sheetId="2" r:id="rId2"/>
+    <sheet name="第二次計算形心_及與樣本的距離" sheetId="3" r:id="rId3"/>
+    <sheet name="第三次計算形心_及與樣本的距離" sheetId="4" r:id="rId4"/>
+    <sheet name="第四次計算形心_及與樣本的距離_產出四個 Outcome" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -722,6 +722,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -735,12 +741,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -867,7 +867,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>工作表5!$H$1</c:f>
+              <c:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -959,7 +959,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>工作表5!$G$2:$G$21</c:f>
+              <c:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$G$2:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1028,7 +1028,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>工作表5!$H$2:$H$21</c:f>
+              <c:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$H$2:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1452,7 +1452,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>工作表5!$H$1</c:f>
+              <c:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2223,7 +2223,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>工作表5!$G$2:$G$21</c:f>
+              <c:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$G$2:$G$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2292,7 +2292,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>工作表5!$H$2:$H$21</c:f>
+              <c:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$H$2:$H$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2363,7 +2363,7 @@
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:datalabelsRange>
-                <c15:f>工作表5!$I$2:$I$21</c15:f>
+                <c15:f>'第四次計算形心_及與樣本的距離_產出四個 Outcome'!$I$2:$I$21</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="20"/>
                   <c:pt idx="0">
@@ -4820,11 +4820,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
       <c r="D1" s="2"/>
       <c r="E1" s="35"/>
       <c r="F1" s="36"/>
@@ -5321,12 +5321,12 @@
         <v>35</v>
       </c>
       <c r="J1" s="2"/>
-      <c r="K1" s="45" t="s">
+      <c r="K1" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
     </row>
@@ -5415,11 +5415,11 @@
         <v>7</v>
       </c>
       <c r="L3" s="13">
-        <f>AVERAGE(工作表2!B2:B8)</f>
+        <f>AVERAGE(第一次計算形心_及與樣本的距離!B2:B8)</f>
         <v>47.857142857142854</v>
       </c>
       <c r="M3" s="14">
-        <f>AVERAGE(工作表2!B9:B15)</f>
+        <f>AVERAGE(第一次計算形心_及與樣本的距離!B9:B15)</f>
         <v>48.714285714285715</v>
       </c>
       <c r="N3" s="13">
@@ -5467,7 +5467,7 @@
         <v>8</v>
       </c>
       <c r="L4" s="13">
-        <f>AVERAGE(工作表2!C2:C8)</f>
+        <f>AVERAGE(第一次計算形心_及與樣本的距離!C2:C8)</f>
         <v>7.7142857142857144</v>
       </c>
       <c r="M4" s="2">
@@ -6288,7 +6288,7 @@
       <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="44" t="s">
         <v>25</v>
       </c>
       <c r="I1" s="7" t="s">
@@ -6307,12 +6307,12 @@
         <v>17</v>
       </c>
       <c r="N1" s="7"/>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="48"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="50"/>
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
     </row>
@@ -7555,7 +7555,7 @@
       <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="44" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -7574,12 +7574,12 @@
         <v>21</v>
       </c>
       <c r="O1" s="2"/>
-      <c r="P1" s="46" t="s">
+      <c r="P1" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="48"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="50"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
     </row>
@@ -8911,7 +8911,7 @@
       <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="45" t="s">
         <v>38</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -8930,12 +8930,12 @@
         <v>27</v>
       </c>
       <c r="O1" s="2"/>
-      <c r="P1" s="45" t="s">
+      <c r="P1" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
     </row>
